--- a/guru99_automation/target/test-classes/testdata/WithdrawalData.xlsx
+++ b/guru99_automation/target/test-classes/testdata/WithdrawalData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahr\eclipse-workspace\wipro-assignment\capstone_guru99\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E7F16E-F6EC-45E8-AF90-12246B193EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8693F1-8BA3-46A4-A7E5-34F734EE3437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WithdrawalData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
   <si>
     <t>AccountID</t>
   </si>
@@ -388,7 +388,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -413,7 +413,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="B4">
         <v>560000</v>
@@ -441,7 +441,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="B6">
         <v>-500</v>
